--- a/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.7.1 Advanced Functions - Filtering with dropdown lists working file.xlsx
+++ b/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.7.1 Advanced Functions - Filtering with dropdown lists working file.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="28810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/travis/Dropbox/Data Handling in Excel/06 Create Dropdowns for Filtering/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rittiv/Documents/GitHub/Projects-Data/1.7. EXCEL  SECTION - Advanced Formulas and Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14628979-6322-424F-8AF5-48E72EC31B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9000" yWindow="1280" windowWidth="25600" windowHeight="14400"/>
+    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dashboard" sheetId="9" r:id="rId1"/>
@@ -22,10 +23,21 @@
     <definedName name="MARKETING_PERF">marketing_perf!$A$1:$H$381</definedName>
     <definedName name="UNIQUE_KEYPHRASES">marketing_perf!$A$1:$A$381</definedName>
   </definedNames>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -35,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="412">
   <si>
     <t>Campaign</t>
   </si>
@@ -1276,14 +1288,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="44" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -1891,7 +1903,7 @@
     <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1899,27 +1911,27 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="21" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="21" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="21" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="21" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="37" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="37" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1927,21 +1939,19 @@
     <xf numFmtId="0" fontId="21" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="34" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="34" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="2" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="2" fillId="35" borderId="0" xfId="48" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="3" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="34" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="3" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="21" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1950,9 +1960,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="26" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="26" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="26" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1967,8 +1977,8 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="27" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="27" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="167" fontId="27" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="27" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
@@ -2020,7 +2030,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Percent" xfId="48" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="48" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -2035,6 +2045,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2326,436 +2339,456 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:N27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" style="30" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="30" customWidth="1"/>
-    <col min="3" max="3" width="15" style="30" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" style="30" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="30" customWidth="1"/>
-    <col min="6" max="6" width="14.1640625" style="30" customWidth="1"/>
-    <col min="7" max="7" width="5.83203125" style="30" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" style="30" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" style="30" customWidth="1"/>
-    <col min="10" max="10" width="15" style="30" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" style="30" customWidth="1"/>
-    <col min="12" max="12" width="10.1640625" style="30" customWidth="1"/>
-    <col min="13" max="13" width="14.1640625" style="30" customWidth="1"/>
-    <col min="14" max="14" width="5.83203125" style="30" customWidth="1"/>
-    <col min="15" max="16384" width="10.83203125" style="30"/>
+    <col min="1" max="1" width="4.33203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="28" customWidth="1"/>
+    <col min="3" max="3" width="15" style="28" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" style="28" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" style="28" customWidth="1"/>
+    <col min="7" max="7" width="5.83203125" style="28" customWidth="1"/>
+    <col min="8" max="8" width="4.6640625" style="28" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" style="28" customWidth="1"/>
+    <col min="10" max="10" width="15" style="28" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" style="28" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" style="28" customWidth="1"/>
+    <col min="13" max="13" width="14.1640625" style="28" customWidth="1"/>
+    <col min="14" max="14" width="5.83203125" style="28" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="28"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B2" s="33"/>
-      <c r="C2" s="41" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="39" t="s">
         <v>409</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="41" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="39" t="s">
         <v>411</v>
       </c>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B3" s="32"/>
-      <c r="C3"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="35" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="32">
+        <f>COUNTIF(marketing_perf!C2:C381,dashboard!$C$3)</f>
+        <v>186</v>
+      </c>
+      <c r="F3" s="33" t="s">
         <v>410</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="42" t="s">
+      <c r="G3" s="29"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="40" t="s">
         <v>410</v>
       </c>
-      <c r="N3" s="31"/>
+      <c r="N3" s="29"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="31"/>
-      <c r="C5" s="37" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="35" t="s">
         <v>381</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="36" t="s">
         <v>399</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="E5" s="36" t="s">
         <v>408</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="36" t="s">
         <v>389</v>
       </c>
-      <c r="G5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="39" t="s">
+      <c r="G5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="37" t="s">
         <v>381</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="38" t="s">
         <v>399</v>
       </c>
-      <c r="L5" s="40" t="s">
+      <c r="L5" s="38" t="s">
         <v>408</v>
       </c>
-      <c r="M5" s="40" t="s">
+      <c r="M5" s="38" t="s">
         <v>389</v>
       </c>
-      <c r="N5" s="31"/>
+      <c r="N5" s="29"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="31"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="31"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="34">
+        <f>SUMIF(marketing_perf!C328:C381,dashboard!$C$3, marketing_perf!H2:H381)</f>
+        <v>6514.78</v>
+      </c>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="29"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B7" s="31"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="N21" s="31"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="31"/>
-      <c r="N22" s="31"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="31"/>
-      <c r="N27" s="31"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2983152A-789B-FE4F-B5AC-B1AEBF02BCD5}">
+          <x14:formula1>
+            <xm:f>signups!$C$3:$I$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>C3</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L381"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2769,7 +2802,7 @@
     <col min="9" max="9" width="13.83203125" style="6" customWidth="1"/>
     <col min="10" max="10" width="14.6640625" style="6" customWidth="1"/>
     <col min="11" max="11" width="13.6640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="13.1640625" style="28" customWidth="1"/>
+    <col min="12" max="12" width="13.1640625" style="10" customWidth="1"/>
     <col min="13" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
@@ -2804,7 +2837,7 @@
       <c r="J1" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="27" t="s">
         <v>405</v>
       </c>
       <c r="L1" s="26" t="s">
@@ -2848,7 +2881,7 @@
         <f>IF(G2&gt;0,G2/F2,"")</f>
         <v>69.233571428571437</v>
       </c>
-      <c r="L2" s="27" t="str">
+      <c r="L2" s="24" t="str">
         <f>IF(ISNUMBER(K2),IF(K2&lt;=75,"Low",IF(K2&lt;=200,"Medium","High")),"Untested")</f>
         <v>Low</v>
       </c>
@@ -2890,7 +2923,7 @@
         <f t="shared" ref="K3:K66" si="2">IF(G3&gt;0,G3/F3,"")</f>
         <v>67.735749999999996</v>
       </c>
-      <c r="L3" s="27" t="str">
+      <c r="L3" s="24" t="str">
         <f t="shared" ref="L3:L66" si="3">IF(ISNUMBER(K3),IF(K3&lt;=75,"Low",IF(K3&lt;=200,"Medium","High")),"Untested")</f>
         <v>Low</v>
       </c>
@@ -2932,7 +2965,7 @@
         <f t="shared" si="2"/>
         <v>87.451111111111103</v>
       </c>
-      <c r="L4" s="27" t="str">
+      <c r="L4" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -2974,7 +3007,7 @@
         <f t="shared" si="2"/>
         <v>57.843333333333334</v>
       </c>
-      <c r="L5" s="27" t="str">
+      <c r="L5" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3016,7 +3049,7 @@
         <f t="shared" si="2"/>
         <v>80.88277777777779</v>
       </c>
-      <c r="L6" s="27" t="str">
+      <c r="L6" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3058,7 +3091,7 @@
         <f t="shared" si="2"/>
         <v>98.569285714285712</v>
       </c>
-      <c r="L7" s="27" t="str">
+      <c r="L7" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3100,7 +3133,7 @@
         <f t="shared" si="2"/>
         <v>239.92</v>
       </c>
-      <c r="L8" s="27" t="str">
+      <c r="L8" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3142,7 +3175,7 @@
         <f t="shared" si="2"/>
         <v>106.47909090909091</v>
       </c>
-      <c r="L9" s="27" t="str">
+      <c r="L9" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3184,7 +3217,7 @@
         <f t="shared" si="2"/>
         <v>66.023750000000007</v>
       </c>
-      <c r="L10" s="27" t="str">
+      <c r="L10" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3226,7 +3259,7 @@
         <f t="shared" si="2"/>
         <v>87.818181818181813</v>
       </c>
-      <c r="L11" s="27" t="str">
+      <c r="L11" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3268,7 +3301,7 @@
         <f t="shared" si="2"/>
         <v>218.75</v>
       </c>
-      <c r="L12" s="27" t="str">
+      <c r="L12" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3310,7 +3343,7 @@
         <f t="shared" si="2"/>
         <v>164.4</v>
       </c>
-      <c r="L13" s="27" t="str">
+      <c r="L13" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3352,7 +3385,7 @@
         <f t="shared" si="2"/>
         <v>53.346000000000004</v>
       </c>
-      <c r="L14" s="27" t="str">
+      <c r="L14" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3394,7 +3427,7 @@
         <f t="shared" si="2"/>
         <v>720</v>
       </c>
-      <c r="L15" s="27" t="str">
+      <c r="L15" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3436,7 +3469,7 @@
         <f t="shared" si="2"/>
         <v>79.734444444444449</v>
       </c>
-      <c r="L16" s="27" t="str">
+      <c r="L16" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3478,7 +3511,7 @@
         <f t="shared" si="2"/>
         <v>88.737499999999997</v>
       </c>
-      <c r="L17" s="27" t="str">
+      <c r="L17" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3520,7 +3553,7 @@
         <f t="shared" si="2"/>
         <v>236.49666666666667</v>
       </c>
-      <c r="L18" s="27" t="str">
+      <c r="L18" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3562,7 +3595,7 @@
         <f t="shared" si="2"/>
         <v>87.185000000000002</v>
       </c>
-      <c r="L19" s="27" t="str">
+      <c r="L19" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3604,7 +3637,7 @@
         <f t="shared" si="2"/>
         <v>105.33333333333333</v>
       </c>
-      <c r="L20" s="27" t="str">
+      <c r="L20" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3646,7 +3679,7 @@
         <f t="shared" si="2"/>
         <v>59.160000000000004</v>
       </c>
-      <c r="L21" s="27" t="str">
+      <c r="L21" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -3688,7 +3721,7 @@
         <f t="shared" si="2"/>
         <v>243.5</v>
       </c>
-      <c r="L22" s="27" t="str">
+      <c r="L22" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3730,7 +3763,7 @@
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
-      <c r="L23" s="27" t="str">
+      <c r="L23" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3772,7 +3805,7 @@
         <f t="shared" si="2"/>
         <v>241.35</v>
       </c>
-      <c r="L24" s="27" t="str">
+      <c r="L24" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3814,7 +3847,7 @@
         <f t="shared" si="2"/>
         <v>117.64749999999999</v>
       </c>
-      <c r="L25" s="27" t="str">
+      <c r="L25" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3856,7 +3889,7 @@
         <f t="shared" si="2"/>
         <v>77.971666666666664</v>
       </c>
-      <c r="L26" s="27" t="str">
+      <c r="L26" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -3898,7 +3931,7 @@
         <f t="shared" si="2"/>
         <v>229</v>
       </c>
-      <c r="L27" s="27" t="str">
+      <c r="L27" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3940,7 +3973,7 @@
         <f t="shared" si="2"/>
         <v>217.5</v>
       </c>
-      <c r="L28" s="27" t="str">
+      <c r="L28" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -3982,7 +4015,7 @@
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="L29" s="27" t="str">
+      <c r="L29" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4024,7 +4057,7 @@
         <f t="shared" si="2"/>
         <v>137.66666666666666</v>
       </c>
-      <c r="L30" s="27" t="str">
+      <c r="L30" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4066,7 +4099,7 @@
         <f t="shared" si="2"/>
         <v>64.583333333333329</v>
       </c>
-      <c r="L31" s="27" t="str">
+      <c r="L31" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4108,7 +4141,7 @@
         <f t="shared" si="2"/>
         <v>96.732500000000002</v>
       </c>
-      <c r="L32" s="27" t="str">
+      <c r="L32" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4150,7 +4183,7 @@
         <f t="shared" si="2"/>
         <v>127.99666666666667</v>
       </c>
-      <c r="L33" s="27" t="str">
+      <c r="L33" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4192,7 +4225,7 @@
         <f t="shared" si="2"/>
         <v>94.49</v>
       </c>
-      <c r="L34" s="27" t="str">
+      <c r="L34" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4234,7 +4267,7 @@
         <f t="shared" si="2"/>
         <v>62.5</v>
       </c>
-      <c r="L35" s="27" t="str">
+      <c r="L35" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4276,7 +4309,7 @@
         <f t="shared" si="2"/>
         <v>92.5</v>
       </c>
-      <c r="L36" s="27" t="str">
+      <c r="L36" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4318,7 +4351,7 @@
         <f t="shared" si="2"/>
         <v>183.5</v>
       </c>
-      <c r="L37" s="27" t="str">
+      <c r="L37" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4360,7 +4393,7 @@
         <f t="shared" si="2"/>
         <v>60.15</v>
       </c>
-      <c r="L38" s="27" t="str">
+      <c r="L38" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4402,7 +4435,7 @@
         <f t="shared" si="2"/>
         <v>58.24666666666667</v>
       </c>
-      <c r="L39" s="27" t="str">
+      <c r="L39" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4444,7 +4477,7 @@
         <f t="shared" si="2"/>
         <v>349</v>
       </c>
-      <c r="L40" s="27" t="str">
+      <c r="L40" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4486,7 +4519,7 @@
         <f t="shared" si="2"/>
         <v>48.042857142857144</v>
       </c>
-      <c r="L41" s="27" t="str">
+      <c r="L41" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4528,7 +4561,7 @@
         <f t="shared" si="2"/>
         <v>166.75</v>
       </c>
-      <c r="L42" s="27" t="str">
+      <c r="L42" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4570,7 +4603,7 @@
         <f t="shared" si="2"/>
         <v>40.712499999999999</v>
       </c>
-      <c r="L43" s="27" t="str">
+      <c r="L43" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4612,7 +4645,7 @@
         <f t="shared" si="2"/>
         <v>78.25</v>
       </c>
-      <c r="L44" s="27" t="str">
+      <c r="L44" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4654,7 +4687,7 @@
         <f t="shared" si="2"/>
         <v>76.872500000000002</v>
       </c>
-      <c r="L45" s="27" t="str">
+      <c r="L45" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4696,7 +4729,7 @@
         <f t="shared" si="2"/>
         <v>149.495</v>
       </c>
-      <c r="L46" s="27" t="str">
+      <c r="L46" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4738,7 +4771,7 @@
         <f t="shared" si="2"/>
         <v>73.547499999999999</v>
       </c>
-      <c r="L47" s="27" t="str">
+      <c r="L47" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4780,7 +4813,7 @@
         <f t="shared" si="2"/>
         <v>92.333333333333329</v>
       </c>
-      <c r="L48" s="27" t="str">
+      <c r="L48" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -4822,7 +4855,7 @@
         <f t="shared" si="2"/>
         <v>53.6</v>
       </c>
-      <c r="L49" s="27" t="str">
+      <c r="L49" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4864,7 +4897,7 @@
         <f t="shared" si="2"/>
         <v>66.75</v>
       </c>
-      <c r="L50" s="27" t="str">
+      <c r="L50" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -4906,7 +4939,7 @@
         <f t="shared" si="2"/>
         <v>262.5</v>
       </c>
-      <c r="L51" s="27" t="str">
+      <c r="L51" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4948,7 +4981,7 @@
         <f t="shared" si="2"/>
         <v>262</v>
       </c>
-      <c r="L52" s="27" t="str">
+      <c r="L52" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -4990,7 +5023,7 @@
         <f t="shared" si="2"/>
         <v>65.424999999999997</v>
       </c>
-      <c r="L53" s="27" t="str">
+      <c r="L53" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -5032,7 +5065,7 @@
         <f t="shared" si="2"/>
         <v>260.91000000000003</v>
       </c>
-      <c r="L54" s="27" t="str">
+      <c r="L54" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -5074,7 +5107,7 @@
         <f t="shared" si="2"/>
         <v>260</v>
       </c>
-      <c r="L55" s="27" t="str">
+      <c r="L55" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -5116,7 +5149,7 @@
         <f t="shared" si="2"/>
         <v>51.9</v>
       </c>
-      <c r="L56" s="27" t="str">
+      <c r="L56" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -5158,7 +5191,7 @@
         <f t="shared" si="2"/>
         <v>259</v>
       </c>
-      <c r="L57" s="27" t="str">
+      <c r="L57" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -5200,7 +5233,7 @@
         <f t="shared" si="2"/>
         <v>258</v>
       </c>
-      <c r="L58" s="27" t="str">
+      <c r="L58" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -5242,7 +5275,7 @@
         <f t="shared" si="2"/>
         <v>250</v>
       </c>
-      <c r="L59" s="27" t="str">
+      <c r="L59" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -5284,7 +5317,7 @@
         <f t="shared" si="2"/>
         <v>82.333333333333329</v>
       </c>
-      <c r="L60" s="27" t="str">
+      <c r="L60" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -5326,7 +5359,7 @@
         <f t="shared" si="2"/>
         <v>80.833333333333329</v>
       </c>
-      <c r="L61" s="27" t="str">
+      <c r="L61" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -5368,7 +5401,7 @@
         <f t="shared" si="2"/>
         <v>59.5</v>
       </c>
-      <c r="L62" s="27" t="str">
+      <c r="L62" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -5410,7 +5443,7 @@
         <f t="shared" si="2"/>
         <v>237</v>
       </c>
-      <c r="L63" s="27" t="str">
+      <c r="L63" s="24" t="str">
         <f t="shared" si="3"/>
         <v>High</v>
       </c>
@@ -5452,7 +5485,7 @@
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
-      <c r="L64" s="27" t="str">
+      <c r="L64" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Medium</v>
       </c>
@@ -5494,7 +5527,7 @@
         <f t="shared" si="2"/>
         <v>74.5</v>
       </c>
-      <c r="L65" s="27" t="str">
+      <c r="L65" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -5536,7 +5569,7 @@
         <f t="shared" si="2"/>
         <v>36.718333333333334</v>
       </c>
-      <c r="L66" s="27" t="str">
+      <c r="L66" s="24" t="str">
         <f t="shared" si="3"/>
         <v>Low</v>
       </c>
@@ -5578,7 +5611,7 @@
         <f t="shared" ref="K67:K130" si="6">IF(G67&gt;0,G67/F67,"")</f>
         <v>70.8</v>
       </c>
-      <c r="L67" s="27" t="str">
+      <c r="L67" s="24" t="str">
         <f t="shared" ref="L67:L130" si="7">IF(ISNUMBER(K67),IF(K67&lt;=75,"Low",IF(K67&lt;=200,"Medium","High")),"Untested")</f>
         <v>Low</v>
       </c>
@@ -5620,7 +5653,7 @@
         <f t="shared" si="6"/>
         <v>70.5</v>
       </c>
-      <c r="L68" s="27" t="str">
+      <c r="L68" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5662,7 +5695,7 @@
         <f t="shared" si="6"/>
         <v>68.526666666666671</v>
       </c>
-      <c r="L69" s="27" t="str">
+      <c r="L69" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -5704,7 +5737,7 @@
         <f t="shared" si="6"/>
         <v>101.99</v>
       </c>
-      <c r="L70" s="27" t="str">
+      <c r="L70" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5746,7 +5779,7 @@
         <f t="shared" si="6"/>
         <v>203.6</v>
       </c>
-      <c r="L71" s="27" t="str">
+      <c r="L71" s="24" t="str">
         <f t="shared" si="7"/>
         <v>High</v>
       </c>
@@ -5788,7 +5821,7 @@
         <f t="shared" si="6"/>
         <v>97.5</v>
       </c>
-      <c r="L72" s="27" t="str">
+      <c r="L72" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5830,7 +5863,7 @@
         <f t="shared" si="6"/>
         <v>188</v>
       </c>
-      <c r="L73" s="27" t="str">
+      <c r="L73" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5872,7 +5905,7 @@
         <f t="shared" si="6"/>
         <v>183</v>
       </c>
-      <c r="L74" s="27" t="str">
+      <c r="L74" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5914,7 +5947,7 @@
         <f t="shared" si="6"/>
         <v>88.495000000000005</v>
       </c>
-      <c r="L75" s="27" t="str">
+      <c r="L75" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5956,7 +5989,7 @@
         <f t="shared" si="6"/>
         <v>170</v>
       </c>
-      <c r="L76" s="27" t="str">
+      <c r="L76" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -5998,7 +6031,7 @@
         <f t="shared" si="6"/>
         <v>162.9</v>
       </c>
-      <c r="L77" s="27" t="str">
+      <c r="L77" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6040,7 +6073,7 @@
         <f t="shared" si="6"/>
         <v>162</v>
       </c>
-      <c r="L78" s="27" t="str">
+      <c r="L78" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6082,7 +6115,7 @@
         <f t="shared" si="6"/>
         <v>40.15</v>
       </c>
-      <c r="L79" s="27" t="str">
+      <c r="L79" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6124,7 +6157,7 @@
         <f t="shared" si="6"/>
         <v>157</v>
       </c>
-      <c r="L80" s="27" t="str">
+      <c r="L80" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6166,7 +6199,7 @@
         <f t="shared" si="6"/>
         <v>30.75</v>
       </c>
-      <c r="L81" s="27" t="str">
+      <c r="L81" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6208,7 +6241,7 @@
         <f t="shared" si="6"/>
         <v>150</v>
       </c>
-      <c r="L82" s="27" t="str">
+      <c r="L82" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6250,7 +6283,7 @@
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="L83" s="27" t="str">
+      <c r="L83" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6292,7 +6325,7 @@
         <f t="shared" si="6"/>
         <v>74.734999999999999</v>
       </c>
-      <c r="L84" s="27" t="str">
+      <c r="L84" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6334,7 +6367,7 @@
         <f t="shared" si="6"/>
         <v>74.5</v>
       </c>
-      <c r="L85" s="27" t="str">
+      <c r="L85" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6376,7 +6409,7 @@
         <f t="shared" si="6"/>
         <v>71.965000000000003</v>
       </c>
-      <c r="L86" s="27" t="str">
+      <c r="L86" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6418,7 +6451,7 @@
         <f t="shared" si="6"/>
         <v>142</v>
       </c>
-      <c r="L87" s="27" t="str">
+      <c r="L87" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6460,7 +6493,7 @@
         <f t="shared" si="6"/>
         <v>139</v>
       </c>
-      <c r="L88" s="27" t="str">
+      <c r="L88" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6502,7 +6535,7 @@
         <f t="shared" si="6"/>
         <v>134</v>
       </c>
-      <c r="L89" s="27" t="str">
+      <c r="L89" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6544,7 +6577,7 @@
         <f t="shared" si="6"/>
         <v>26.7</v>
       </c>
-      <c r="L90" s="27" t="str">
+      <c r="L90" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6586,7 +6619,7 @@
         <f t="shared" si="6"/>
         <v>132</v>
       </c>
-      <c r="L91" s="27" t="str">
+      <c r="L91" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6628,7 +6661,7 @@
         <f t="shared" si="6"/>
         <v>65.125</v>
       </c>
-      <c r="L92" s="27" t="str">
+      <c r="L92" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6670,7 +6703,7 @@
         <f t="shared" si="6"/>
         <v>43.143333333333338</v>
       </c>
-      <c r="L93" s="27" t="str">
+      <c r="L93" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6712,7 +6745,7 @@
         <f t="shared" si="6"/>
         <v>127.2</v>
       </c>
-      <c r="L94" s="27" t="str">
+      <c r="L94" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6754,7 +6787,7 @@
         <f t="shared" si="6"/>
         <v>62</v>
       </c>
-      <c r="L95" s="27" t="str">
+      <c r="L95" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6796,7 +6829,7 @@
         <f t="shared" si="6"/>
         <v>61.5</v>
       </c>
-      <c r="L96" s="27" t="str">
+      <c r="L96" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6838,7 +6871,7 @@
         <f t="shared" si="6"/>
         <v>58.9</v>
       </c>
-      <c r="L97" s="27" t="str">
+      <c r="L97" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -6880,7 +6913,7 @@
         <f t="shared" si="6"/>
         <v>115</v>
       </c>
-      <c r="L98" s="27" t="str">
+      <c r="L98" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6922,7 +6955,7 @@
         <f t="shared" si="6"/>
         <v>113</v>
       </c>
-      <c r="L99" s="27" t="str">
+      <c r="L99" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -6964,7 +6997,7 @@
         <f t="shared" si="6"/>
         <v>113</v>
       </c>
-      <c r="L100" s="27" t="str">
+      <c r="L100" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7006,7 +7039,7 @@
         <f t="shared" si="6"/>
         <v>111.6</v>
       </c>
-      <c r="L101" s="27" t="str">
+      <c r="L101" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7048,7 +7081,7 @@
         <f t="shared" si="6"/>
         <v>109</v>
       </c>
-      <c r="L102" s="27" t="str">
+      <c r="L102" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7090,7 +7123,7 @@
         <f t="shared" si="6"/>
         <v>103.5</v>
       </c>
-      <c r="L103" s="27" t="str">
+      <c r="L103" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7132,7 +7165,7 @@
         <f t="shared" si="6"/>
         <v>51</v>
       </c>
-      <c r="L104" s="27" t="str">
+      <c r="L104" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7174,7 +7207,7 @@
         <f t="shared" si="6"/>
         <v>101.5</v>
       </c>
-      <c r="L105" s="27" t="str">
+      <c r="L105" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7216,7 +7249,7 @@
         <f t="shared" si="6"/>
         <v>33.016666666666666</v>
       </c>
-      <c r="L106" s="27" t="str">
+      <c r="L106" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7258,7 +7291,7 @@
         <f t="shared" si="6"/>
         <v>99</v>
       </c>
-      <c r="L107" s="27" t="str">
+      <c r="L107" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7300,7 +7333,7 @@
         <f t="shared" si="6"/>
         <v>99</v>
       </c>
-      <c r="L108" s="27" t="str">
+      <c r="L108" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7342,7 +7375,7 @@
         <f t="shared" si="6"/>
         <v>47.994999999999997</v>
       </c>
-      <c r="L109" s="27" t="str">
+      <c r="L109" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7384,7 +7417,7 @@
         <f t="shared" si="6"/>
         <v>31.99</v>
       </c>
-      <c r="L110" s="27" t="str">
+      <c r="L110" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7426,7 +7459,7 @@
         <f t="shared" si="6"/>
         <v>94</v>
       </c>
-      <c r="L111" s="27" t="str">
+      <c r="L111" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7468,7 +7501,7 @@
         <f t="shared" si="6"/>
         <v>94</v>
       </c>
-      <c r="L112" s="27" t="str">
+      <c r="L112" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7510,7 +7543,7 @@
         <f t="shared" si="6"/>
         <v>46.49</v>
       </c>
-      <c r="L113" s="27" t="str">
+      <c r="L113" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7552,7 +7585,7 @@
         <f t="shared" si="6"/>
         <v>92</v>
       </c>
-      <c r="L114" s="27" t="str">
+      <c r="L114" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7594,7 +7627,7 @@
         <f t="shared" si="6"/>
         <v>92</v>
       </c>
-      <c r="L115" s="27" t="str">
+      <c r="L115" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7636,7 +7669,7 @@
         <f t="shared" si="6"/>
         <v>45.5</v>
       </c>
-      <c r="L116" s="27" t="str">
+      <c r="L116" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7678,7 +7711,7 @@
         <f t="shared" si="6"/>
         <v>45.5</v>
       </c>
-      <c r="L117" s="27" t="str">
+      <c r="L117" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -7720,7 +7753,7 @@
         <f t="shared" si="6"/>
         <v>89.98</v>
       </c>
-      <c r="L118" s="27" t="str">
+      <c r="L118" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7762,7 +7795,7 @@
         <f t="shared" si="6"/>
         <v>89.5</v>
       </c>
-      <c r="L119" s="27" t="str">
+      <c r="L119" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7804,7 +7837,7 @@
         <f t="shared" si="6"/>
         <v>88</v>
       </c>
-      <c r="L120" s="27" t="str">
+      <c r="L120" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7846,7 +7879,7 @@
         <f t="shared" si="6"/>
         <v>88</v>
       </c>
-      <c r="L121" s="27" t="str">
+      <c r="L121" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7888,7 +7921,7 @@
         <f t="shared" si="6"/>
         <v>88</v>
       </c>
-      <c r="L122" s="27" t="str">
+      <c r="L122" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7930,7 +7963,7 @@
         <f t="shared" si="6"/>
         <v>87</v>
       </c>
-      <c r="L123" s="27" t="str">
+      <c r="L123" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -7972,7 +8005,7 @@
         <f t="shared" si="6"/>
         <v>29</v>
       </c>
-      <c r="L124" s="27" t="str">
+      <c r="L124" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -8014,7 +8047,7 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="L125" s="27" t="str">
+      <c r="L125" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -8056,7 +8089,7 @@
         <f t="shared" si="6"/>
         <v>85.92</v>
       </c>
-      <c r="L126" s="27" t="str">
+      <c r="L126" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -8098,7 +8131,7 @@
         <f t="shared" si="6"/>
         <v>42.825000000000003</v>
       </c>
-      <c r="L127" s="27" t="str">
+      <c r="L127" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Low</v>
       </c>
@@ -8140,7 +8173,7 @@
         <f t="shared" si="6"/>
         <v>84</v>
       </c>
-      <c r="L128" s="27" t="str">
+      <c r="L128" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -8182,7 +8215,7 @@
         <f t="shared" si="6"/>
         <v>83</v>
       </c>
-      <c r="L129" s="27" t="str">
+      <c r="L129" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -8224,7 +8257,7 @@
         <f t="shared" si="6"/>
         <v>82</v>
       </c>
-      <c r="L130" s="27" t="str">
+      <c r="L130" s="24" t="str">
         <f t="shared" si="7"/>
         <v>Medium</v>
       </c>
@@ -8266,7 +8299,7 @@
         <f t="shared" ref="K131:K194" si="10">IF(G131&gt;0,G131/F131,"")</f>
         <v>80</v>
       </c>
-      <c r="L131" s="27" t="str">
+      <c r="L131" s="24" t="str">
         <f t="shared" ref="L131:L194" si="11">IF(ISNUMBER(K131),IF(K131&lt;=75,"Low",IF(K131&lt;=200,"Medium","High")),"Untested")</f>
         <v>Medium</v>
       </c>
@@ -8308,7 +8341,7 @@
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="L132" s="27" t="str">
+      <c r="L132" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8350,7 +8383,7 @@
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="L133" s="27" t="str">
+      <c r="L133" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8392,7 +8425,7 @@
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="L134" s="27" t="str">
+      <c r="L134" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8434,7 +8467,7 @@
         <f t="shared" si="10"/>
         <v>79</v>
       </c>
-      <c r="L135" s="27" t="str">
+      <c r="L135" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8476,7 +8509,7 @@
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="L136" s="27" t="str">
+      <c r="L136" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8518,7 +8551,7 @@
         <f t="shared" si="10"/>
         <v>78</v>
       </c>
-      <c r="L137" s="27" t="str">
+      <c r="L137" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8560,7 +8593,7 @@
         <f t="shared" si="10"/>
         <v>77.5</v>
       </c>
-      <c r="L138" s="27" t="str">
+      <c r="L138" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8602,7 +8635,7 @@
         <f t="shared" si="10"/>
         <v>76</v>
       </c>
-      <c r="L139" s="27" t="str">
+      <c r="L139" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8644,7 +8677,7 @@
         <f t="shared" si="10"/>
         <v>75.98</v>
       </c>
-      <c r="L140" s="27" t="str">
+      <c r="L140" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Medium</v>
       </c>
@@ -8686,7 +8719,7 @@
         <f t="shared" si="10"/>
         <v>37.5</v>
       </c>
-      <c r="L141" s="27" t="str">
+      <c r="L141" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8728,7 +8761,7 @@
         <f t="shared" si="10"/>
         <v>75</v>
       </c>
-      <c r="L142" s="27" t="str">
+      <c r="L142" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8770,7 +8803,7 @@
         <f t="shared" si="10"/>
         <v>74</v>
       </c>
-      <c r="L143" s="27" t="str">
+      <c r="L143" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8812,7 +8845,7 @@
         <f t="shared" si="10"/>
         <v>74</v>
       </c>
-      <c r="L144" s="27" t="str">
+      <c r="L144" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8854,7 +8887,7 @@
         <f t="shared" si="10"/>
         <v>37</v>
       </c>
-      <c r="L145" s="27" t="str">
+      <c r="L145" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8896,7 +8929,7 @@
         <f t="shared" si="10"/>
         <v>72.98</v>
       </c>
-      <c r="L146" s="27" t="str">
+      <c r="L146" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8938,7 +8971,7 @@
         <f t="shared" si="10"/>
         <v>69.989999999999995</v>
       </c>
-      <c r="L147" s="27" t="str">
+      <c r="L147" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -8980,7 +9013,7 @@
         <f t="shared" si="10"/>
         <v>68</v>
       </c>
-      <c r="L148" s="27" t="str">
+      <c r="L148" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9022,7 +9055,7 @@
         <f t="shared" si="10"/>
         <v>67</v>
       </c>
-      <c r="L149" s="27" t="str">
+      <c r="L149" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9064,7 +9097,7 @@
         <f t="shared" si="10"/>
         <v>64</v>
       </c>
-      <c r="L150" s="27" t="str">
+      <c r="L150" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9106,7 +9139,7 @@
         <f t="shared" si="10"/>
         <v>63.6</v>
       </c>
-      <c r="L151" s="27" t="str">
+      <c r="L151" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9148,7 +9181,7 @@
         <f t="shared" si="10"/>
         <v>63.5</v>
       </c>
-      <c r="L152" s="27" t="str">
+      <c r="L152" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9190,7 +9223,7 @@
         <f t="shared" si="10"/>
         <v>63</v>
       </c>
-      <c r="L153" s="27" t="str">
+      <c r="L153" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9232,7 +9265,7 @@
         <f t="shared" si="10"/>
         <v>63</v>
       </c>
-      <c r="L154" s="27" t="str">
+      <c r="L154" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9274,7 +9307,7 @@
         <f t="shared" si="10"/>
         <v>62</v>
       </c>
-      <c r="L155" s="27" t="str">
+      <c r="L155" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9316,7 +9349,7 @@
         <f t="shared" si="10"/>
         <v>31</v>
       </c>
-      <c r="L156" s="27" t="str">
+      <c r="L156" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9358,7 +9391,7 @@
         <f t="shared" si="10"/>
         <v>20.400000000000002</v>
       </c>
-      <c r="L157" s="27" t="str">
+      <c r="L157" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9400,7 +9433,7 @@
         <f t="shared" si="10"/>
         <v>30.5</v>
       </c>
-      <c r="L158" s="27" t="str">
+      <c r="L158" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9442,7 +9475,7 @@
         <f t="shared" si="10"/>
         <v>61</v>
       </c>
-      <c r="L159" s="27" t="str">
+      <c r="L159" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9484,7 +9517,7 @@
         <f t="shared" si="10"/>
         <v>60</v>
       </c>
-      <c r="L160" s="27" t="str">
+      <c r="L160" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9526,7 +9559,7 @@
         <f t="shared" si="10"/>
         <v>59</v>
       </c>
-      <c r="L161" s="27" t="str">
+      <c r="L161" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9568,7 +9601,7 @@
         <f t="shared" si="10"/>
         <v>58.5</v>
       </c>
-      <c r="L162" s="27" t="str">
+      <c r="L162" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9610,7 +9643,7 @@
         <f t="shared" si="10"/>
         <v>58</v>
       </c>
-      <c r="L163" s="27" t="str">
+      <c r="L163" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9652,7 +9685,7 @@
         <f t="shared" si="10"/>
         <v>57</v>
       </c>
-      <c r="L164" s="27" t="str">
+      <c r="L164" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9694,7 +9727,7 @@
         <f t="shared" si="10"/>
         <v>56.8</v>
       </c>
-      <c r="L165" s="27" t="str">
+      <c r="L165" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9736,7 +9769,7 @@
         <f t="shared" si="10"/>
         <v>55.96</v>
       </c>
-      <c r="L166" s="27" t="str">
+      <c r="L166" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9778,7 +9811,7 @@
         <f t="shared" si="10"/>
         <v>55.5</v>
       </c>
-      <c r="L167" s="27" t="str">
+      <c r="L167" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9820,7 +9853,7 @@
         <f t="shared" si="10"/>
         <v>55.3</v>
       </c>
-      <c r="L168" s="27" t="str">
+      <c r="L168" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9862,7 +9895,7 @@
         <f t="shared" si="10"/>
         <v>55</v>
       </c>
-      <c r="L169" s="27" t="str">
+      <c r="L169" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9904,7 +9937,7 @@
         <f t="shared" si="10"/>
         <v>55</v>
       </c>
-      <c r="L170" s="27" t="str">
+      <c r="L170" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9946,7 +9979,7 @@
         <f t="shared" si="10"/>
         <v>54</v>
       </c>
-      <c r="L171" s="27" t="str">
+      <c r="L171" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -9988,7 +10021,7 @@
         <f t="shared" si="10"/>
         <v>52</v>
       </c>
-      <c r="L172" s="27" t="str">
+      <c r="L172" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10030,7 +10063,7 @@
         <f t="shared" si="10"/>
         <v>51</v>
       </c>
-      <c r="L173" s="27" t="str">
+      <c r="L173" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10072,7 +10105,7 @@
         <f t="shared" si="10"/>
         <v>50.99</v>
       </c>
-      <c r="L174" s="27" t="str">
+      <c r="L174" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10114,7 +10147,7 @@
         <f t="shared" si="10"/>
         <v>50</v>
       </c>
-      <c r="L175" s="27" t="str">
+      <c r="L175" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10156,7 +10189,7 @@
         <f t="shared" si="10"/>
         <v>25</v>
       </c>
-      <c r="L176" s="27" t="str">
+      <c r="L176" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10198,7 +10231,7 @@
         <f t="shared" si="10"/>
         <v>50</v>
       </c>
-      <c r="L177" s="27" t="str">
+      <c r="L177" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10240,7 +10273,7 @@
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
-      <c r="L178" s="27" t="str">
+      <c r="L178" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10282,7 +10315,7 @@
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
-      <c r="L179" s="27" t="str">
+      <c r="L179" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10324,7 +10357,7 @@
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
-      <c r="L180" s="27" t="str">
+      <c r="L180" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10366,7 +10399,7 @@
         <f t="shared" si="10"/>
         <v>49</v>
       </c>
-      <c r="L181" s="27" t="str">
+      <c r="L181" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10408,7 +10441,7 @@
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="L182" s="27" t="str">
+      <c r="L182" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10450,7 +10483,7 @@
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="L183" s="27" t="str">
+      <c r="L183" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10492,7 +10525,7 @@
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
-      <c r="L184" s="27" t="str">
+      <c r="L184" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10534,7 +10567,7 @@
         <f t="shared" si="10"/>
         <v>45</v>
       </c>
-      <c r="L185" s="27" t="str">
+      <c r="L185" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10576,7 +10609,7 @@
         <f t="shared" si="10"/>
         <v>44.75</v>
       </c>
-      <c r="L186" s="27" t="str">
+      <c r="L186" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10618,7 +10651,7 @@
         <f t="shared" si="10"/>
         <v>44</v>
       </c>
-      <c r="L187" s="27" t="str">
+      <c r="L187" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10660,7 +10693,7 @@
         <f t="shared" si="10"/>
         <v>43</v>
       </c>
-      <c r="L188" s="27" t="str">
+      <c r="L188" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10702,7 +10735,7 @@
         <f t="shared" si="10"/>
         <v>42.98</v>
       </c>
-      <c r="L189" s="27" t="str">
+      <c r="L189" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10744,7 +10777,7 @@
         <f t="shared" si="10"/>
         <v>20.245000000000001</v>
       </c>
-      <c r="L190" s="27" t="str">
+      <c r="L190" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10786,7 +10819,7 @@
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="L191" s="27" t="str">
+      <c r="L191" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10828,7 +10861,7 @@
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="L192" s="27" t="str">
+      <c r="L192" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10870,7 +10903,7 @@
         <f t="shared" si="10"/>
         <v>40</v>
       </c>
-      <c r="L193" s="27" t="str">
+      <c r="L193" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10912,7 +10945,7 @@
         <f t="shared" si="10"/>
         <v>39</v>
       </c>
-      <c r="L194" s="27" t="str">
+      <c r="L194" s="24" t="str">
         <f t="shared" si="11"/>
         <v>Low</v>
       </c>
@@ -10954,7 +10987,7 @@
         <f t="shared" ref="K195:K258" si="14">IF(G195&gt;0,G195/F195,"")</f>
         <v>39</v>
       </c>
-      <c r="L195" s="27" t="str">
+      <c r="L195" s="24" t="str">
         <f t="shared" ref="L195:L258" si="15">IF(ISNUMBER(K195),IF(K195&lt;=75,"Low",IF(K195&lt;=200,"Medium","High")),"Untested")</f>
         <v>Low</v>
       </c>
@@ -10996,7 +11029,7 @@
         <f t="shared" si="14"/>
         <v>38.49</v>
       </c>
-      <c r="L196" s="27" t="str">
+      <c r="L196" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11038,7 +11071,7 @@
         <f t="shared" si="14"/>
         <v>38</v>
       </c>
-      <c r="L197" s="27" t="str">
+      <c r="L197" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11080,7 +11113,7 @@
         <f t="shared" si="14"/>
         <v>38</v>
       </c>
-      <c r="L198" s="27" t="str">
+      <c r="L198" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11122,7 +11155,7 @@
         <f t="shared" si="14"/>
         <v>37.5</v>
       </c>
-      <c r="L199" s="27" t="str">
+      <c r="L199" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11164,7 +11197,7 @@
         <f t="shared" si="14"/>
         <v>36.369999999999997</v>
       </c>
-      <c r="L200" s="27" t="str">
+      <c r="L200" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11206,7 +11239,7 @@
         <f t="shared" si="14"/>
         <v>36</v>
       </c>
-      <c r="L201" s="27" t="str">
+      <c r="L201" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11248,7 +11281,7 @@
         <f t="shared" si="14"/>
         <v>35.49</v>
       </c>
-      <c r="L202" s="27" t="str">
+      <c r="L202" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11290,7 +11323,7 @@
         <f t="shared" si="14"/>
         <v>35</v>
       </c>
-      <c r="L203" s="27" t="str">
+      <c r="L203" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11332,7 +11365,7 @@
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
-      <c r="L204" s="27" t="str">
+      <c r="L204" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11374,7 +11407,7 @@
         <f t="shared" si="14"/>
         <v>31.49</v>
       </c>
-      <c r="L205" s="27" t="str">
+      <c r="L205" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11416,7 +11449,7 @@
         <f t="shared" si="14"/>
         <v>31</v>
       </c>
-      <c r="L206" s="27" t="str">
+      <c r="L206" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11458,7 +11491,7 @@
         <f t="shared" si="14"/>
         <v>29</v>
       </c>
-      <c r="L207" s="27" t="str">
+      <c r="L207" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11500,7 +11533,7 @@
         <f t="shared" si="14"/>
         <v>28</v>
       </c>
-      <c r="L208" s="27" t="str">
+      <c r="L208" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11542,7 +11575,7 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L209" s="27" t="str">
+      <c r="L209" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11584,7 +11617,7 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L210" s="27" t="str">
+      <c r="L210" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11626,7 +11659,7 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L211" s="27" t="str">
+      <c r="L211" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11668,7 +11701,7 @@
         <f t="shared" si="14"/>
         <v>27</v>
       </c>
-      <c r="L212" s="27" t="str">
+      <c r="L212" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11710,7 +11743,7 @@
         <f t="shared" si="14"/>
         <v>26</v>
       </c>
-      <c r="L213" s="27" t="str">
+      <c r="L213" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11752,7 +11785,7 @@
         <f t="shared" si="14"/>
         <v>26</v>
       </c>
-      <c r="L214" s="27" t="str">
+      <c r="L214" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11794,7 +11827,7 @@
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L215" s="27" t="str">
+      <c r="L215" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11836,7 +11869,7 @@
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L216" s="27" t="str">
+      <c r="L216" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11878,7 +11911,7 @@
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L217" s="27" t="str">
+      <c r="L217" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11920,7 +11953,7 @@
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
-      <c r="L218" s="27" t="str">
+      <c r="L218" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -11962,7 +11995,7 @@
         <f t="shared" si="14"/>
         <v>24</v>
       </c>
-      <c r="L219" s="27" t="str">
+      <c r="L219" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12004,7 +12037,7 @@
         <f t="shared" si="14"/>
         <v>23</v>
       </c>
-      <c r="L220" s="27" t="str">
+      <c r="L220" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12046,7 +12079,7 @@
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
-      <c r="L221" s="27" t="str">
+      <c r="L221" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12088,7 +12121,7 @@
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
-      <c r="L222" s="27" t="str">
+      <c r="L222" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12130,7 +12163,7 @@
         <f t="shared" si="14"/>
         <v>22</v>
       </c>
-      <c r="L223" s="27" t="str">
+      <c r="L223" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12172,7 +12205,7 @@
         <f t="shared" si="14"/>
         <v>20.99</v>
       </c>
-      <c r="L224" s="27" t="str">
+      <c r="L224" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12214,7 +12247,7 @@
         <f t="shared" si="14"/>
         <v>18.61</v>
       </c>
-      <c r="L225" s="27" t="str">
+      <c r="L225" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12256,7 +12289,7 @@
         <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="L226" s="27" t="str">
+      <c r="L226" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12298,7 +12331,7 @@
         <f t="shared" si="14"/>
         <v>18</v>
       </c>
-      <c r="L227" s="27" t="str">
+      <c r="L227" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12340,7 +12373,7 @@
         <f t="shared" si="14"/>
         <v>17.989999999999998</v>
       </c>
-      <c r="L228" s="27" t="str">
+      <c r="L228" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12382,7 +12415,7 @@
         <f t="shared" si="14"/>
         <v>15.5</v>
       </c>
-      <c r="L229" s="27" t="str">
+      <c r="L229" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12424,7 +12457,7 @@
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
-      <c r="L230" s="27" t="str">
+      <c r="L230" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12466,7 +12499,7 @@
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
-      <c r="L231" s="27" t="str">
+      <c r="L231" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12508,7 +12541,7 @@
         <f t="shared" si="14"/>
         <v>12.5</v>
       </c>
-      <c r="L232" s="27" t="str">
+      <c r="L232" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12550,7 +12583,7 @@
         <f t="shared" si="14"/>
         <v>11.4</v>
       </c>
-      <c r="L233" s="27" t="str">
+      <c r="L233" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12592,7 +12625,7 @@
         <f t="shared" si="14"/>
         <v>8.5</v>
       </c>
-      <c r="L234" s="27" t="str">
+      <c r="L234" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12634,7 +12667,7 @@
         <f t="shared" si="14"/>
         <v>8.5</v>
       </c>
-      <c r="L235" s="27" t="str">
+      <c r="L235" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12676,7 +12709,7 @@
         <f t="shared" si="14"/>
         <v>7.97</v>
       </c>
-      <c r="L236" s="27" t="str">
+      <c r="L236" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12718,7 +12751,7 @@
         <f t="shared" si="14"/>
         <v>7.97</v>
       </c>
-      <c r="L237" s="27" t="str">
+      <c r="L237" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12760,7 +12793,7 @@
         <f t="shared" si="14"/>
         <v>7.8</v>
       </c>
-      <c r="L238" s="27" t="str">
+      <c r="L238" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12802,7 +12835,7 @@
         <f t="shared" si="14"/>
         <v>5.99</v>
       </c>
-      <c r="L239" s="27" t="str">
+      <c r="L239" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Low</v>
       </c>
@@ -12844,7 +12877,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L240" s="27" t="str">
+      <c r="L240" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -12886,7 +12919,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L241" s="27" t="str">
+      <c r="L241" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -12928,7 +12961,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L242" s="27" t="str">
+      <c r="L242" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -12970,7 +13003,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L243" s="27" t="str">
+      <c r="L243" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13012,7 +13045,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L244" s="27" t="str">
+      <c r="L244" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13054,7 +13087,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L245" s="27" t="str">
+      <c r="L245" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13096,7 +13129,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L246" s="27" t="str">
+      <c r="L246" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13138,7 +13171,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L247" s="27" t="str">
+      <c r="L247" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13180,7 +13213,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L248" s="27" t="str">
+      <c r="L248" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13222,7 +13255,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L249" s="27" t="str">
+      <c r="L249" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13264,7 +13297,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L250" s="27" t="str">
+      <c r="L250" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13306,7 +13339,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L251" s="27" t="str">
+      <c r="L251" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13348,7 +13381,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L252" s="27" t="str">
+      <c r="L252" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13390,7 +13423,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L253" s="27" t="str">
+      <c r="L253" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13432,7 +13465,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L254" s="27" t="str">
+      <c r="L254" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13474,7 +13507,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L255" s="27" t="str">
+      <c r="L255" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13516,7 +13549,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L256" s="27" t="str">
+      <c r="L256" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13558,7 +13591,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L257" s="27" t="str">
+      <c r="L257" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13600,7 +13633,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L258" s="27" t="str">
+      <c r="L258" s="24" t="str">
         <f t="shared" si="15"/>
         <v>Untested</v>
       </c>
@@ -13642,7 +13675,7 @@
         <f t="shared" ref="K259:K322" si="18">IF(G259&gt;0,G259/F259,"")</f>
         <v/>
       </c>
-      <c r="L259" s="27" t="str">
+      <c r="L259" s="24" t="str">
         <f t="shared" ref="L259:L322" si="19">IF(ISNUMBER(K259),IF(K259&lt;=75,"Low",IF(K259&lt;=200,"Medium","High")),"Untested")</f>
         <v>Untested</v>
       </c>
@@ -13684,7 +13717,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L260" s="27" t="str">
+      <c r="L260" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -13726,7 +13759,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L261" s="27" t="str">
+      <c r="L261" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -13768,7 +13801,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L262" s="27" t="str">
+      <c r="L262" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -13810,7 +13843,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L263" s="27" t="str">
+      <c r="L263" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -13852,7 +13885,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L264" s="27" t="str">
+      <c r="L264" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -13894,7 +13927,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L265" s="27" t="str">
+      <c r="L265" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -13936,7 +13969,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L266" s="27" t="str">
+      <c r="L266" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -13978,7 +14011,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L267" s="27" t="str">
+      <c r="L267" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14020,7 +14053,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L268" s="27" t="str">
+      <c r="L268" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14062,7 +14095,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L269" s="27" t="str">
+      <c r="L269" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14104,7 +14137,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L270" s="27" t="str">
+      <c r="L270" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14146,7 +14179,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L271" s="27" t="str">
+      <c r="L271" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14188,7 +14221,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L272" s="27" t="str">
+      <c r="L272" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14230,7 +14263,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L273" s="27" t="str">
+      <c r="L273" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14272,7 +14305,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L274" s="27" t="str">
+      <c r="L274" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14314,7 +14347,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L275" s="27" t="str">
+      <c r="L275" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14356,7 +14389,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L276" s="27" t="str">
+      <c r="L276" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14398,7 +14431,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L277" s="27" t="str">
+      <c r="L277" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14440,7 +14473,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L278" s="27" t="str">
+      <c r="L278" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14482,7 +14515,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L279" s="27" t="str">
+      <c r="L279" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14524,7 +14557,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L280" s="27" t="str">
+      <c r="L280" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14566,7 +14599,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L281" s="27" t="str">
+      <c r="L281" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14608,7 +14641,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L282" s="27" t="str">
+      <c r="L282" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14650,7 +14683,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L283" s="27" t="str">
+      <c r="L283" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14692,7 +14725,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L284" s="27" t="str">
+      <c r="L284" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14734,7 +14767,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L285" s="27" t="str">
+      <c r="L285" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14776,7 +14809,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L286" s="27" t="str">
+      <c r="L286" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14818,7 +14851,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L287" s="27" t="str">
+      <c r="L287" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14860,7 +14893,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L288" s="27" t="str">
+      <c r="L288" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14902,7 +14935,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L289" s="27" t="str">
+      <c r="L289" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14944,7 +14977,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L290" s="27" t="str">
+      <c r="L290" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -14986,7 +15019,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L291" s="27" t="str">
+      <c r="L291" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15028,7 +15061,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L292" s="27" t="str">
+      <c r="L292" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15070,7 +15103,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L293" s="27" t="str">
+      <c r="L293" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15112,7 +15145,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L294" s="27" t="str">
+      <c r="L294" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15154,7 +15187,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L295" s="27" t="str">
+      <c r="L295" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15196,7 +15229,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L296" s="27" t="str">
+      <c r="L296" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15238,7 +15271,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L297" s="27" t="str">
+      <c r="L297" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15280,7 +15313,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L298" s="27" t="str">
+      <c r="L298" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15322,7 +15355,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L299" s="27" t="str">
+      <c r="L299" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15364,7 +15397,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L300" s="27" t="str">
+      <c r="L300" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15406,7 +15439,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L301" s="27" t="str">
+      <c r="L301" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15448,7 +15481,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L302" s="27" t="str">
+      <c r="L302" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15490,7 +15523,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L303" s="27" t="str">
+      <c r="L303" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15532,7 +15565,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L304" s="27" t="str">
+      <c r="L304" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15574,7 +15607,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L305" s="27" t="str">
+      <c r="L305" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15616,7 +15649,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L306" s="27" t="str">
+      <c r="L306" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15658,7 +15691,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L307" s="27" t="str">
+      <c r="L307" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15700,7 +15733,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L308" s="27" t="str">
+      <c r="L308" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15742,7 +15775,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L309" s="27" t="str">
+      <c r="L309" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15784,7 +15817,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L310" s="27" t="str">
+      <c r="L310" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15826,7 +15859,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L311" s="27" t="str">
+      <c r="L311" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15868,7 +15901,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L312" s="27" t="str">
+      <c r="L312" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15910,7 +15943,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L313" s="27" t="str">
+      <c r="L313" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15952,7 +15985,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L314" s="27" t="str">
+      <c r="L314" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -15994,7 +16027,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L315" s="27" t="str">
+      <c r="L315" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -16036,7 +16069,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L316" s="27" t="str">
+      <c r="L316" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -16078,7 +16111,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L317" s="27" t="str">
+      <c r="L317" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -16120,7 +16153,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L318" s="27" t="str">
+      <c r="L318" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -16162,7 +16195,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L319" s="27" t="str">
+      <c r="L319" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -16204,7 +16237,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L320" s="27" t="str">
+      <c r="L320" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -16246,7 +16279,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L321" s="27" t="str">
+      <c r="L321" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -16288,7 +16321,7 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L322" s="27" t="str">
+      <c r="L322" s="24" t="str">
         <f t="shared" si="19"/>
         <v>Untested</v>
       </c>
@@ -16330,7 +16363,7 @@
         <f t="shared" ref="K323:K381" si="22">IF(G323&gt;0,G323/F323,"")</f>
         <v/>
       </c>
-      <c r="L323" s="27" t="str">
+      <c r="L323" s="24" t="str">
         <f t="shared" ref="L323:L381" si="23">IF(ISNUMBER(K323),IF(K323&lt;=75,"Low",IF(K323&lt;=200,"Medium","High")),"Untested")</f>
         <v>Untested</v>
       </c>
@@ -16372,7 +16405,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L324" s="27" t="str">
+      <c r="L324" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16414,7 +16447,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L325" s="27" t="str">
+      <c r="L325" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16456,7 +16489,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L326" s="27" t="str">
+      <c r="L326" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16498,7 +16531,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L327" s="27" t="str">
+      <c r="L327" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16540,7 +16573,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L328" s="27" t="str">
+      <c r="L328" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16582,7 +16615,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L329" s="27" t="str">
+      <c r="L329" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16624,7 +16657,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L330" s="27" t="str">
+      <c r="L330" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16666,7 +16699,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L331" s="27" t="str">
+      <c r="L331" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16708,7 +16741,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L332" s="27" t="str">
+      <c r="L332" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16750,7 +16783,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L333" s="27" t="str">
+      <c r="L333" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16792,7 +16825,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L334" s="27" t="str">
+      <c r="L334" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16834,7 +16867,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L335" s="27" t="str">
+      <c r="L335" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16876,7 +16909,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L336" s="27" t="str">
+      <c r="L336" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16918,7 +16951,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L337" s="27" t="str">
+      <c r="L337" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -16960,7 +16993,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L338" s="27" t="str">
+      <c r="L338" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17002,7 +17035,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L339" s="27" t="str">
+      <c r="L339" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17044,7 +17077,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L340" s="27" t="str">
+      <c r="L340" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17086,7 +17119,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L341" s="27" t="str">
+      <c r="L341" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17128,7 +17161,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L342" s="27" t="str">
+      <c r="L342" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17170,7 +17203,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L343" s="27" t="str">
+      <c r="L343" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17212,7 +17245,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L344" s="27" t="str">
+      <c r="L344" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17254,7 +17287,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L345" s="27" t="str">
+      <c r="L345" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17296,7 +17329,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L346" s="27" t="str">
+      <c r="L346" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17338,7 +17371,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L347" s="27" t="str">
+      <c r="L347" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17380,7 +17413,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L348" s="27" t="str">
+      <c r="L348" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17422,7 +17455,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L349" s="27" t="str">
+      <c r="L349" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17464,7 +17497,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L350" s="27" t="str">
+      <c r="L350" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17506,7 +17539,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L351" s="27" t="str">
+      <c r="L351" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17548,7 +17581,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L352" s="27" t="str">
+      <c r="L352" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17590,7 +17623,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L353" s="27" t="str">
+      <c r="L353" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17632,7 +17665,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L354" s="27" t="str">
+      <c r="L354" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17674,7 +17707,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L355" s="27" t="str">
+      <c r="L355" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17716,7 +17749,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L356" s="27" t="str">
+      <c r="L356" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17758,7 +17791,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L357" s="27" t="str">
+      <c r="L357" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17800,7 +17833,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L358" s="27" t="str">
+      <c r="L358" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17842,7 +17875,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L359" s="27" t="str">
+      <c r="L359" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17884,7 +17917,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L360" s="27" t="str">
+      <c r="L360" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17926,7 +17959,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L361" s="27" t="str">
+      <c r="L361" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -17968,7 +18001,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L362" s="27" t="str">
+      <c r="L362" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18010,7 +18043,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L363" s="27" t="str">
+      <c r="L363" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18052,7 +18085,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L364" s="27" t="str">
+      <c r="L364" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18094,7 +18127,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L365" s="27" t="str">
+      <c r="L365" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18136,7 +18169,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L366" s="27" t="str">
+      <c r="L366" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18178,7 +18211,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L367" s="27" t="str">
+      <c r="L367" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18220,7 +18253,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L368" s="27" t="str">
+      <c r="L368" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18262,7 +18295,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L369" s="27" t="str">
+      <c r="L369" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18304,7 +18337,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L370" s="27" t="str">
+      <c r="L370" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18346,7 +18379,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L371" s="27" t="str">
+      <c r="L371" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18388,7 +18421,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L372" s="27" t="str">
+      <c r="L372" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18430,7 +18463,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L373" s="27" t="str">
+      <c r="L373" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18472,7 +18505,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L374" s="27" t="str">
+      <c r="L374" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18514,7 +18547,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L375" s="27" t="str">
+      <c r="L375" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18556,7 +18589,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L376" s="27" t="str">
+      <c r="L376" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18598,7 +18631,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L377" s="27" t="str">
+      <c r="L377" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18640,7 +18673,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L378" s="27" t="str">
+      <c r="L378" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18682,7 +18715,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L379" s="27" t="str">
+      <c r="L379" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18724,7 +18757,7 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L380" s="27" t="str">
+      <c r="L380" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
@@ -18766,13 +18799,13 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L381" s="27" t="str">
+      <c r="L381" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Untested</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:H383">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H383">
     <sortCondition descending="1" ref="G2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18780,7 +18813,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -18843,7 +18876,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="44" t="s">
         <v>401</v>
       </c>
       <c r="B4" s="12" t="s">
@@ -18880,7 +18913,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="46"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="12" t="s">
         <v>237</v>
       </c>
@@ -18921,7 +18954,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="12" t="s">
         <v>22</v>
       </c>
@@ -18960,7 +18993,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="46"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="12" t="s">
         <v>388</v>
       </c>
@@ -18995,7 +19028,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="46"/>
+      <c r="A8" s="44"/>
       <c r="B8" s="12" t="s">
         <v>386</v>
       </c>
@@ -19038,7 +19071,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="46"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="12" t="s">
         <v>400</v>
       </c>
